--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationstatement.xlsx
@@ -81,13 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このProfileは服薬状況を示すものであり，診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
+    <t>このProfileは服薬状況を示すものであり、診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や，調剤情報，薬剤投与実施情報としては用いられず，それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
+    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や、調剤情報、薬剤投与実施情報としては用いられず、それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -501,7 +501,7 @@
   </si>
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。それ以外に任意のIDを付与してもよい。
-このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -969,7 +969,7 @@
 </t>
   </si>
   <si>
-    <t>投与理由，対象疾患についてのコード</t>
+    <t>投与理由、対象疾患についてのコード</t>
   </si>
   <si>
     <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
@@ -1062,7 +1062,7 @@
 </t>
   </si>
   <si>
-    <t>この薬剤がどのように服用されたのか，服用すべきだったのかを示す情報</t>
+    <t>この薬剤がどのように服用されたのか、服用すべきだったのかを示す情報</t>
   </si>
   <si>
     <t>患者にこの薬剤がどのように服用すべきかを示す情報</t>
